--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89819299</v>
+        <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>91923</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormossen, Gstr</t>
+          <t>Söder om Kårsberget, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584222</v>
+        <v>584201</v>
       </c>
       <c r="R2" t="n">
-        <v>6695112</v>
+        <v>6695210</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>AXN0025 Calluna AB</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,49 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819299</t>
+          <t>https://artportalen.se/Sighting/136866009</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89819297</v>
+        <v>89819299</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584199</v>
+        <v>584222</v>
       </c>
       <c r="R3" t="n">
-        <v>6695146</v>
+        <v>6695112</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,16 +897,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819297</t>
+          <t>https://artportalen.se/Sighting/89819299</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89819298</v>
+        <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>96565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,41 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormossen, Gstr</t>
+          <t>Söder om Kårsberget, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584206</v>
+        <v>584148</v>
       </c>
       <c r="R4" t="n">
-        <v>6695122</v>
+        <v>6695298</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>AXN0025 Calluna AB</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,24 +998,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819298</t>
+          <t>https://artportalen.se/Sighting/136866012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89819300</v>
+        <v>89819297</v>
       </c>
       <c r="B5" t="n">
         <v>91872</v>
@@ -1052,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584212</v>
+        <v>584199</v>
       </c>
       <c r="R5" t="n">
-        <v>6695113</v>
+        <v>6695146</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,38 +1120,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819300</t>
+          <t>https://artportalen.se/Sighting/89819297</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61520601</v>
+        <v>89819298</v>
       </c>
       <c r="B6" t="n">
-        <v>43426</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100942</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,35 +1159,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baggå, Gstr</t>
+          <t>Stormossen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583875</v>
+        <v>584206</v>
       </c>
       <c r="R6" t="n">
-        <v>6695351</v>
+        <v>6695122</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,27 +1195,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-08-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0% sol (dvs mulet), N vind 4-6 m/s, 15 °C</t>
+          <t>AXN0025 Calluna AB</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,67 +1216,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kraftledning</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Ängsvädd</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61520601</t>
+          <t>https://artportalen.se/Sighting/89819298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61520603</v>
+        <v>89819300</v>
       </c>
       <c r="B7" t="n">
-        <v>43426</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100942</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1308,35 +1270,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Baggå, Gstr</t>
+          <t>Stormossen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583877</v>
+        <v>584212</v>
       </c>
       <c r="R7" t="n">
-        <v>6695346</v>
+        <v>6695113</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,27 +1306,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-08-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-08-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0% sol (dvs mulet), N vind 4-6 m/s, 15 °C</t>
+          <t>AXN0025 Calluna AB</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,42 +1327,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kraftledning</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Ängsvädd</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61520603</t>
+          <t>https://artportalen.se/Sighting/89819300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120618392</v>
+        <v>61520601</v>
       </c>
       <c r="B8" t="n">
         <v>43426</v>
@@ -1469,6 +1391,7 @@
           <t>larv/nymf</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1480,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583874</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6695353</v>
+        <v>6695351</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1510,27 +1433,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>23 grader varmt, lätt molnighet, 3-5 m/s, sydllig vind, 90% sol. Under sista halvan av sommaren har det kommit väldigt lite nederbörd. Bäcken som korsar lokalen var helt uttorkad. Vitmossan som finns på lokalen var vit på grund av att den saknade fukt.</t>
+          <t>0% sol (dvs mulet), N vind 4-6 m/s, 15 °C</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,6 +1468,11 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Kraftledning</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Ängsvädd</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1565,13 +1493,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120618392</t>
+          <t>https://artportalen.se/Sighting/61520601</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120618393</v>
+        <v>61520603</v>
       </c>
       <c r="B9" t="n">
         <v>43426</v>
@@ -1614,6 +1542,7 @@
           <t>larv/nymf</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1628,7 +1557,7 @@
         <v>583877</v>
       </c>
       <c r="R9" t="n">
-        <v>6695355</v>
+        <v>6695346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1655,27 +1584,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>23 grader varmt, lätt molnighet, 3-5 m/s, sydllig vind, 90% sol. Under sista halvan av sommaren har det kommit väldigt lite nederbörd. Bäcken som korsar lokalen var helt uttorkad. Vitmossan som finns på lokalen var vit på grund av att den saknade fukt.</t>
+          <t>0% sol (dvs mulet), N vind 4-6 m/s, 15 °C</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,6 +1619,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Kraftledning</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Ängsvädd</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1710,13 +1644,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120618393</t>
+          <t>https://artportalen.se/Sighting/61520603</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120618394</v>
+        <v>120618392</v>
       </c>
       <c r="B10" t="n">
         <v>43426</v>
@@ -1770,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583878</v>
+        <v>583874</v>
       </c>
       <c r="R10" t="n">
-        <v>6695355</v>
+        <v>6695353</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1855,38 +1789,38 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120618394</t>
+          <t>https://artportalen.se/Sighting/120618392</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89819286</v>
+        <v>120618393</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>43426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100942</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1894,19 +1828,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormossen, Gstr</t>
+          <t>Baggå, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584079</v>
+        <v>583877</v>
       </c>
       <c r="R11" t="n">
-        <v>6695165</v>
+        <v>6695355</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1930,17 +1879,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>AXN0025 Calluna AB</t>
+          <t>23 grader varmt, lätt molnighet, 3-5 m/s, sydllig vind, 90% sol. Under sista halvan av sommaren har det kommit väldigt lite nederbörd. Bäcken som korsar lokalen var helt uttorkad. Vitmossan som finns på lokalen var vit på grund av att den saknade fukt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,53 +1910,62 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kraftledning</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819286</t>
+          <t>https://artportalen.se/Sighting/120618393</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89819287</v>
+        <v>120618394</v>
       </c>
       <c r="B12" t="n">
-        <v>99035</v>
+        <v>43426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100942</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2005,19 +1973,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormossen, Gstr</t>
+          <t>Baggå, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584154</v>
+        <v>583878</v>
       </c>
       <c r="R12" t="n">
-        <v>6695065</v>
+        <v>6695355</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2041,17 +2024,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>AXN0025 Calluna AB</t>
+          <t>23 grader varmt, lätt molnighet, 3-5 m/s, sydllig vind, 90% sol. Under sista halvan av sommaren har det kommit väldigt lite nederbörd. Bäcken som korsar lokalen var helt uttorkad. Vitmossan som finns på lokalen var vit på grund av att den saknade fukt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2062,28 +2055,37 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kraftledning</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819287</t>
+          <t>https://artportalen.se/Sighting/120618394</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89819290</v>
+        <v>89819286</v>
       </c>
       <c r="B13" t="n">
         <v>99035</v>
@@ -2122,10 +2124,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584161</v>
+        <v>584079</v>
       </c>
       <c r="R13" t="n">
-        <v>6694997</v>
+        <v>6695165</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2188,16 +2190,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89819290</t>
+          <t>https://artportalen.se/Sighting/89819286</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89819288</v>
+        <v>89819287</v>
       </c>
       <c r="B14" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,21 +2207,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2233,10 +2235,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584162</v>
+        <v>584154</v>
       </c>
       <c r="R14" t="n">
-        <v>6695060</v>
+        <v>6695065</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2298,6 +2300,465 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89819287</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89819290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>584161</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6694997</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>AXN0025 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89819290</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136866005</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söder om Kårsberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584159</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6695145</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866005</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136866008</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Söder om Kårsberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584169</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6695211</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89819288</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584162</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6695060</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>AXN0025 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89819288</t>
         </is>
@@ -2318,6 +2779,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35941-2026 artfynd.xlsx
+++ b/artfynd/A 35941-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136866009</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136866012</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136866005</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>136866008</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
